--- a/backend/data/financials_by_company/1560.HK.xlsx
+++ b/backend/data/financials_by_company/1560.HK.xlsx
@@ -657,55 +657,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-208560.79</v>
+        <v>546645</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008337000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>-439540000</v>
+        <v>-16464000</v>
       </c>
       <c r="E2" t="n">
-        <v>-25015000</v>
+        <v>3313000</v>
       </c>
       <c r="F2" t="n">
-        <v>-25015000</v>
+        <v>3313000</v>
       </c>
       <c r="G2" t="n">
-        <v>-605029000</v>
+        <v>-37134000</v>
       </c>
       <c r="H2" t="n">
-        <v>2402000</v>
+        <v>3434000</v>
       </c>
       <c r="I2" t="n">
-        <v>1409929000</v>
+        <v>15751000</v>
       </c>
       <c r="J2" t="n">
-        <v>-464555000</v>
+        <v>-13151000</v>
       </c>
       <c r="K2" t="n">
-        <v>-466957000</v>
+        <v>-16585000</v>
       </c>
       <c r="L2" t="n">
-        <v>-142852000</v>
+        <v>-19210000</v>
       </c>
       <c r="M2" t="n">
-        <v>143423000</v>
+        <v>19416000</v>
       </c>
       <c r="N2" t="n">
-        <v>571000</v>
+        <v>206000</v>
       </c>
       <c r="O2" t="n">
-        <v>-580222560.79</v>
+        <v>-39900355</v>
       </c>
       <c r="P2" t="n">
-        <v>-605029000</v>
+        <v>-37134000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1562049000</v>
+        <v>117407000</v>
       </c>
       <c r="R2" t="n">
         <v>641498000</v>
@@ -714,421 +714,423 @@
         <v>641498000</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9432</v>
+        <v>-0.0579</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9432</v>
+        <v>-0.0579</v>
       </c>
       <c r="V2" t="n">
-        <v>-605029000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>-37134000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
       <c r="X2" t="n">
-        <v>-605029000</v>
+        <v>-37134000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-605029000</v>
+        <v>-37134000</v>
       </c>
       <c r="AA2" t="n">
-        <v>262000</v>
+        <v>412000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-605291000</v>
+        <v>-37546000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-605291000</v>
+        <v>-37546000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-5089000</v>
+        <v>1545000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-610380000</v>
+        <v>-36001000</v>
       </c>
       <c r="AF2" t="n">
-        <v>21593000</v>
+        <v>27395000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-16862000</v>
+        <v>2168000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-2030000</v>
+        <v>-2168000</v>
       </c>
       <c r="AI2" t="n">
-        <v>18892000</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-142852000</v>
+        <v>-19210000</v>
       </c>
       <c r="AK2" t="n">
-        <v>143423000</v>
+        <v>19416000</v>
       </c>
       <c r="AL2" t="n">
-        <v>571000</v>
+        <v>206000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-428975000</v>
+        <v>-38971000</v>
       </c>
       <c r="AN2" t="n">
-        <v>152120000</v>
+        <v>101656000</v>
       </c>
       <c r="AO2" t="n">
-        <v>152120000</v>
+        <v>101656000</v>
       </c>
       <c r="AP2" t="n">
-        <v>80669000</v>
+        <v>3737000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>71451000</v>
+        <v>97919000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-276855000</v>
+        <v>62685000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1409929000</v>
+        <v>15751000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1133074000</v>
+        <v>78436000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1133074000</v>
+        <v>78436000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-68290.23753699999</v>
+        <v>-2572390.695416</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009851</v>
+        <v>0.111799</v>
       </c>
       <c r="D3" t="n">
-        <v>-197561000</v>
+        <v>419423000</v>
       </c>
       <c r="E3" t="n">
-        <v>-6932000</v>
+        <v>-23009000</v>
       </c>
       <c r="F3" t="n">
-        <v>-6932000</v>
+        <v>-23009000</v>
       </c>
       <c r="G3" t="n">
-        <v>-294595000</v>
+        <v>329933000</v>
       </c>
       <c r="H3" t="n">
-        <v>2687000</v>
+        <v>4434000</v>
       </c>
       <c r="I3" t="n">
-        <v>1243833000</v>
+        <v>1089207000</v>
       </c>
       <c r="J3" t="n">
-        <v>-204493000</v>
+        <v>396414000</v>
       </c>
       <c r="K3" t="n">
-        <v>-207180000</v>
+        <v>391980000</v>
       </c>
       <c r="L3" t="n">
-        <v>-91162000</v>
+        <v>-18785000</v>
       </c>
       <c r="M3" t="n">
-        <v>93994000</v>
+        <v>19196000</v>
       </c>
       <c r="N3" t="n">
-        <v>2832000</v>
+        <v>411000</v>
       </c>
       <c r="O3" t="n">
-        <v>-287731290.237537</v>
+        <v>350369609.304584</v>
       </c>
       <c r="P3" t="n">
-        <v>-294595000</v>
+        <v>329933000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1401251000</v>
+        <v>1323839000</v>
       </c>
       <c r="R3" t="n">
-        <v>641498000</v>
+        <v>1477498000</v>
       </c>
       <c r="S3" t="n">
         <v>641498000</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4592</v>
+        <v>0.244</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4592</v>
+        <v>0.5143</v>
       </c>
       <c r="V3" t="n">
-        <v>-294595000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>360567000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>30634000</v>
+      </c>
       <c r="X3" t="n">
-        <v>-294595000</v>
+        <v>329933000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-294595000</v>
+        <v>329933000</v>
       </c>
       <c r="AA3" t="n">
-        <v>3612000</v>
+        <v>-1174000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-298207000</v>
+        <v>331107000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-298207000</v>
+        <v>331107000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2967000</v>
+        <v>41677000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-301174000</v>
+        <v>372784000</v>
       </c>
       <c r="AF3" t="n">
-        <v>24958000</v>
+        <v>29790000</v>
       </c>
       <c r="AG3" t="n">
-        <v>35000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-35000</v>
-      </c>
+        <v>564000</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-564000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-91162000</v>
+        <v>-18785000</v>
       </c>
       <c r="AK3" t="n">
-        <v>93994000</v>
+        <v>19196000</v>
       </c>
       <c r="AL3" t="n">
-        <v>2832000</v>
+        <v>411000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-157541000</v>
+        <v>375465000</v>
       </c>
       <c r="AN3" t="n">
-        <v>157418000</v>
+        <v>234632000</v>
       </c>
       <c r="AO3" t="n">
-        <v>157418000</v>
+        <v>236387000</v>
       </c>
       <c r="AP3" t="n">
-        <v>46631000</v>
+        <v>56825000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>110787000</v>
+        <v>179562000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-123000</v>
+        <v>610097000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1243833000</v>
+        <v>1089207000</v>
       </c>
       <c r="AT3" t="n">
-        <v>1243710000</v>
+        <v>1699304000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1243710000</v>
+        <v>1699304000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-2572390.695416</v>
+        <v>-68290.23753699999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.111799</v>
+        <v>0.009851</v>
       </c>
       <c r="D4" t="n">
-        <v>419423000</v>
+        <v>-197561000</v>
       </c>
       <c r="E4" t="n">
-        <v>-23009000</v>
+        <v>-6932000</v>
       </c>
       <c r="F4" t="n">
-        <v>-23009000</v>
+        <v>-6932000</v>
       </c>
       <c r="G4" t="n">
-        <v>329933000</v>
+        <v>-294595000</v>
       </c>
       <c r="H4" t="n">
-        <v>4434000</v>
+        <v>2687000</v>
       </c>
       <c r="I4" t="n">
-        <v>1089207000</v>
+        <v>1243833000</v>
       </c>
       <c r="J4" t="n">
-        <v>396414000</v>
+        <v>-204493000</v>
       </c>
       <c r="K4" t="n">
-        <v>391980000</v>
+        <v>-207180000</v>
       </c>
       <c r="L4" t="n">
-        <v>-18785000</v>
+        <v>-91162000</v>
       </c>
       <c r="M4" t="n">
-        <v>19196000</v>
+        <v>93994000</v>
       </c>
       <c r="N4" t="n">
-        <v>411000</v>
+        <v>2832000</v>
       </c>
       <c r="O4" t="n">
-        <v>350369609.304584</v>
+        <v>-287731290.237537</v>
       </c>
       <c r="P4" t="n">
-        <v>329933000</v>
+        <v>-294595000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1323839000</v>
+        <v>1401251000</v>
       </c>
       <c r="R4" t="n">
-        <v>1477498000</v>
+        <v>641498000</v>
       </c>
       <c r="S4" t="n">
         <v>641498000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.244</v>
+        <v>-0.4592</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5143</v>
+        <v>-0.4592</v>
       </c>
       <c r="V4" t="n">
-        <v>360567000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>30634000</v>
-      </c>
+        <v>-294595000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>329933000</v>
+        <v>-294595000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>329933000</v>
+        <v>-294595000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1174000</v>
+        <v>3612000</v>
       </c>
       <c r="AB4" t="n">
-        <v>331107000</v>
+        <v>-298207000</v>
       </c>
       <c r="AC4" t="n">
-        <v>331107000</v>
+        <v>-298207000</v>
       </c>
       <c r="AD4" t="n">
-        <v>41677000</v>
+        <v>-2967000</v>
       </c>
       <c r="AE4" t="n">
-        <v>372784000</v>
+        <v>-301174000</v>
       </c>
       <c r="AF4" t="n">
-        <v>29790000</v>
+        <v>24958000</v>
       </c>
       <c r="AG4" t="n">
-        <v>564000</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>35000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-35000</v>
+      </c>
       <c r="AI4" t="n">
-        <v>-564000</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-18785000</v>
+        <v>-91162000</v>
       </c>
       <c r="AK4" t="n">
-        <v>19196000</v>
+        <v>93994000</v>
       </c>
       <c r="AL4" t="n">
-        <v>411000</v>
+        <v>2832000</v>
       </c>
       <c r="AM4" t="n">
-        <v>375465000</v>
+        <v>-157541000</v>
       </c>
       <c r="AN4" t="n">
-        <v>234632000</v>
+        <v>157418000</v>
       </c>
       <c r="AO4" t="n">
-        <v>236387000</v>
+        <v>157418000</v>
       </c>
       <c r="AP4" t="n">
-        <v>56825000</v>
+        <v>46631000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>179562000</v>
+        <v>110787000</v>
       </c>
       <c r="AR4" t="n">
-        <v>610097000</v>
+        <v>-123000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1089207000</v>
+        <v>1243833000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1699304000</v>
+        <v>1243710000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1699304000</v>
+        <v>1243710000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>546645</v>
+        <v>-208560.79</v>
       </c>
       <c r="C5" t="n">
-        <v>0.165</v>
+        <v>0.008337000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>-16464000</v>
+        <v>-439540000</v>
       </c>
       <c r="E5" t="n">
-        <v>3313000</v>
+        <v>-25015000</v>
       </c>
       <c r="F5" t="n">
-        <v>3313000</v>
+        <v>-25015000</v>
       </c>
       <c r="G5" t="n">
-        <v>-37134000</v>
+        <v>-605029000</v>
       </c>
       <c r="H5" t="n">
-        <v>3434000</v>
+        <v>2402000</v>
       </c>
       <c r="I5" t="n">
-        <v>15751000</v>
+        <v>1409929000</v>
       </c>
       <c r="J5" t="n">
-        <v>-13151000</v>
+        <v>-464555000</v>
       </c>
       <c r="K5" t="n">
-        <v>-16585000</v>
+        <v>-466957000</v>
       </c>
       <c r="L5" t="n">
-        <v>-19210000</v>
+        <v>-142852000</v>
       </c>
       <c r="M5" t="n">
-        <v>19416000</v>
+        <v>143423000</v>
       </c>
       <c r="N5" t="n">
-        <v>206000</v>
+        <v>571000</v>
       </c>
       <c r="O5" t="n">
-        <v>-39900355</v>
+        <v>-580222560.79</v>
       </c>
       <c r="P5" t="n">
-        <v>-37134000</v>
+        <v>-605029000</v>
       </c>
       <c r="Q5" t="n">
-        <v>117407000</v>
+        <v>1562049000</v>
       </c>
       <c r="R5" t="n">
         <v>641498000</v>
@@ -1137,88 +1139,86 @@
         <v>641498000</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0579</v>
+        <v>-0.9432</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0579</v>
+        <v>-0.9432</v>
       </c>
       <c r="V5" t="n">
-        <v>-37134000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
+        <v>-605029000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-37134000</v>
+        <v>-605029000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-37134000</v>
+        <v>-605029000</v>
       </c>
       <c r="AA5" t="n">
-        <v>412000</v>
+        <v>262000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-37546000</v>
+        <v>-605291000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-37546000</v>
+        <v>-605291000</v>
       </c>
       <c r="AD5" t="n">
-        <v>1545000</v>
+        <v>-5089000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-36001000</v>
+        <v>-610380000</v>
       </c>
       <c r="AF5" t="n">
-        <v>27395000</v>
+        <v>21593000</v>
       </c>
       <c r="AG5" t="n">
-        <v>2168000</v>
+        <v>-16862000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-2168000</v>
+        <v>-2030000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>18892000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-19210000</v>
+        <v>-142852000</v>
       </c>
       <c r="AK5" t="n">
-        <v>19416000</v>
+        <v>143423000</v>
       </c>
       <c r="AL5" t="n">
-        <v>206000</v>
+        <v>571000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-38971000</v>
+        <v>-428975000</v>
       </c>
       <c r="AN5" t="n">
-        <v>101656000</v>
+        <v>152120000</v>
       </c>
       <c r="AO5" t="n">
-        <v>101656000</v>
+        <v>152120000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3737000</v>
+        <v>80669000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>97919000</v>
+        <v>71451000</v>
       </c>
       <c r="AR5" t="n">
-        <v>62685000</v>
+        <v>-276855000</v>
       </c>
       <c r="AS5" t="n">
-        <v>15751000</v>
+        <v>1409929000</v>
       </c>
       <c r="AT5" t="n">
-        <v>78436000</v>
+        <v>1133074000</v>
       </c>
       <c r="AU5" t="n">
-        <v>78436000</v>
+        <v>1133074000</v>
       </c>
     </row>
   </sheetData>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>641498000</v>
@@ -1578,46 +1578,46 @@
         <v>641498000</v>
       </c>
       <c r="D2" t="n">
-        <v>1270485000</v>
+        <v>3229715000</v>
       </c>
       <c r="E2" t="n">
-        <v>1344646000</v>
+        <v>3381231000</v>
       </c>
       <c r="F2" t="n">
-        <v>817538000</v>
+        <v>1391955000</v>
       </c>
       <c r="G2" t="n">
-        <v>2116878000</v>
+        <v>4715710000</v>
       </c>
       <c r="H2" t="n">
-        <v>95712000</v>
+        <v>1545528000</v>
       </c>
       <c r="I2" t="n">
-        <v>817538000</v>
+        <v>1391955000</v>
       </c>
       <c r="J2" t="n">
-        <v>45306000</v>
+        <v>57476000</v>
       </c>
       <c r="K2" t="n">
-        <v>817538000</v>
+        <v>1391955000</v>
       </c>
       <c r="L2" t="n">
-        <v>892449000</v>
+        <v>2576056000</v>
       </c>
       <c r="M2" t="n">
-        <v>801469000</v>
+        <v>1382256000</v>
       </c>
       <c r="N2" t="n">
-        <v>-16069000</v>
+        <v>-9699000</v>
       </c>
       <c r="O2" t="n">
-        <v>817538000</v>
+        <v>1391955000</v>
       </c>
       <c r="P2" t="n">
-        <v>514667000</v>
+        <v>514124000</v>
       </c>
       <c r="Q2" t="n">
-        <v>225353000</v>
+        <v>791676000</v>
       </c>
       <c r="R2" t="n">
         <v>233457000</v>
@@ -1629,142 +1629,150 @@
         <v>6415000</v>
       </c>
       <c r="U2" t="n">
-        <v>1675247000</v>
+        <v>3918848000</v>
       </c>
       <c r="V2" t="n">
-        <v>152001000</v>
+        <v>1283710000</v>
       </c>
       <c r="W2" t="n">
-        <v>48417000</v>
+        <v>59839000</v>
       </c>
       <c r="X2" t="n">
-        <v>103584000</v>
+        <v>1223871000</v>
       </c>
       <c r="Y2" t="n">
-        <v>28673000</v>
+        <v>39770000</v>
       </c>
       <c r="Z2" t="n">
-        <v>74911000</v>
+        <v>1184101000</v>
       </c>
       <c r="AA2" t="n">
-        <v>1523246000</v>
+        <v>2635138000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1241062000</v>
+        <v>2157360000</v>
       </c>
       <c r="AC2" t="n">
-        <v>16633000</v>
+        <v>17706000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1224429000</v>
+        <v>2139654000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1270000</v>
+        <v>2411000</v>
       </c>
       <c r="AF2" t="n">
-        <v>115714000</v>
+        <v>169336000</v>
       </c>
       <c r="AG2" t="n">
-        <v>82580000</v>
+        <v>142773000</v>
       </c>
       <c r="AH2" t="n">
-        <v>258000</v>
+        <v>128000</v>
       </c>
       <c r="AI2" t="n">
-        <v>32876000</v>
+        <v>26435000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2476716000</v>
+        <v>5301104000</v>
       </c>
       <c r="AK2" t="n">
-        <v>857758000</v>
+        <v>1120438000</v>
       </c>
       <c r="AL2" t="n">
-        <v>3880000</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>5627000</v>
+        <v>3005000</v>
       </c>
       <c r="AN2" t="n">
-        <v>53047000</v>
+        <v>6873000</v>
       </c>
       <c r="AO2" t="n">
-        <v>53047000</v>
+        <v>6873000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6316000</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>6316000</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>738379000</v>
+        <v>1054096000</v>
       </c>
       <c r="AT2" t="n">
-        <v>2656000</v>
+        <v>3416000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-19371000</v>
+        <v>-11629000</v>
       </c>
       <c r="AV2" t="n">
-        <v>22027000</v>
+        <v>15045000</v>
       </c>
       <c r="AW2" t="n">
-        <v>9136000</v>
+        <v>7765000</v>
       </c>
       <c r="AX2" t="n">
-        <v>12891000</v>
+        <v>7280000</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1618958000</v>
+        <v>4180666000</v>
       </c>
       <c r="BA2" t="n">
-        <v>16223000</v>
+        <v>82243000</v>
       </c>
       <c r="BB2" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
+        <v>10403000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>24402000</v>
+      </c>
       <c r="BD2" t="n">
-        <v>1515764000</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
+        <v>3878883000</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>7056000</v>
+      </c>
       <c r="BF2" t="n">
-        <v>1515764000</v>
+        <v>3878883000</v>
       </c>
       <c r="BG2" t="n">
-        <v>3000</v>
+        <v>41897000</v>
       </c>
       <c r="BH2" t="n">
-        <v>29000</v>
+        <v>609000</v>
       </c>
       <c r="BI2" t="n">
-        <v>46132000</v>
-      </c>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
+        <v>5064000</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-1617000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>5064000</v>
+      </c>
       <c r="BL2" t="n">
-        <v>30807000</v>
+        <v>129008000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1952000</v>
+        <v>34968000</v>
       </c>
       <c r="BN2" t="n">
-        <v>28855000</v>
+        <v>94040000</v>
       </c>
       <c r="BO2" t="n">
-        <v>28855000</v>
+        <v>94040000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>641498000</v>
@@ -1773,46 +1781,46 @@
         <v>641498000</v>
       </c>
       <c r="D3" t="n">
-        <v>2174059000</v>
+        <v>2781117000</v>
       </c>
       <c r="E3" t="n">
-        <v>2271214000</v>
+        <v>2885583000</v>
       </c>
       <c r="F3" t="n">
-        <v>1430083000</v>
+        <v>1729525000</v>
       </c>
       <c r="G3" t="n">
-        <v>3651061000</v>
+        <v>4568143000</v>
       </c>
       <c r="H3" t="n">
-        <v>730754000</v>
+        <v>797353000</v>
       </c>
       <c r="I3" t="n">
-        <v>1430083000</v>
+        <v>1729525000</v>
       </c>
       <c r="J3" t="n">
-        <v>50236000</v>
+        <v>46965000</v>
       </c>
       <c r="K3" t="n">
-        <v>1430083000</v>
+        <v>1729525000</v>
       </c>
       <c r="L3" t="n">
-        <v>1525234000</v>
+        <v>1817733000</v>
       </c>
       <c r="M3" t="n">
-        <v>1414276000</v>
+        <v>1717330000</v>
       </c>
       <c r="N3" t="n">
-        <v>-15807000</v>
+        <v>-12195000</v>
       </c>
       <c r="O3" t="n">
-        <v>1430083000</v>
+        <v>1729525000</v>
       </c>
       <c r="P3" t="n">
-        <v>516129000</v>
+        <v>516315000</v>
       </c>
       <c r="Q3" t="n">
-        <v>828920000</v>
+        <v>1123329000</v>
       </c>
       <c r="R3" t="n">
         <v>233457000</v>
@@ -1824,142 +1832,144 @@
         <v>6415000</v>
       </c>
       <c r="U3" t="n">
-        <v>2607928000</v>
+        <v>3390778000</v>
       </c>
       <c r="V3" t="n">
-        <v>181578000</v>
+        <v>174919000</v>
       </c>
       <c r="W3" t="n">
-        <v>52156000</v>
+        <v>54691000</v>
       </c>
       <c r="X3" t="n">
-        <v>129422000</v>
+        <v>120228000</v>
       </c>
       <c r="Y3" t="n">
-        <v>34271000</v>
+        <v>32020000</v>
       </c>
       <c r="Z3" t="n">
-        <v>95151000</v>
+        <v>88208000</v>
       </c>
       <c r="AA3" t="n">
-        <v>2426350000</v>
+        <v>3215859000</v>
       </c>
       <c r="AB3" t="n">
-        <v>2141792000</v>
+        <v>2765355000</v>
       </c>
       <c r="AC3" t="n">
-        <v>15965000</v>
+        <v>14945000</v>
       </c>
       <c r="AD3" t="n">
-        <v>2125827000</v>
+        <v>2750410000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2442000</v>
+        <v>1780000</v>
       </c>
       <c r="AF3" t="n">
-        <v>141030000</v>
+        <v>227790000</v>
       </c>
       <c r="AG3" t="n">
-        <v>96513000</v>
+        <v>157508000</v>
       </c>
       <c r="AH3" t="n">
-        <v>330000</v>
+        <v>14914000</v>
       </c>
       <c r="AI3" t="n">
-        <v>44187000</v>
+        <v>55368000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4022204000</v>
+        <v>5108108000</v>
       </c>
       <c r="AK3" t="n">
-        <v>865100000</v>
+        <v>1094896000</v>
       </c>
       <c r="AL3" t="n">
-        <v>3935000</v>
+        <v>102426000</v>
       </c>
       <c r="AM3" t="n">
-        <v>4377000</v>
+        <v>4029000</v>
       </c>
       <c r="AN3" t="n">
-        <v>5160000</v>
+        <v>6129000</v>
       </c>
       <c r="AO3" t="n">
-        <v>5160000</v>
+        <v>6129000</v>
       </c>
       <c r="AP3" t="n">
-        <v>9967000</v>
+        <v>15424000</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>9967000</v>
+        <v>15424000</v>
       </c>
       <c r="AS3" t="n">
-        <v>776584000</v>
+        <v>883038000</v>
       </c>
       <c r="AT3" t="n">
-        <v>4957000</v>
+        <v>4745000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-16982000</v>
+        <v>-14663000</v>
       </c>
       <c r="AV3" t="n">
-        <v>21939000</v>
+        <v>19408000</v>
       </c>
       <c r="AW3" t="n">
-        <v>9048000</v>
+        <v>11038000</v>
       </c>
       <c r="AX3" t="n">
-        <v>12891000</v>
+        <v>8370000</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3157104000</v>
+        <v>4013212000</v>
       </c>
       <c r="BA3" t="n">
-        <v>31242000</v>
+        <v>17916000</v>
       </c>
       <c r="BB3" t="n">
         <v>10000000</v>
       </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>2913815000</v>
-      </c>
-      <c r="BE3" t="inlineStr"/>
+        <v>3852402000</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>10808000</v>
+      </c>
       <c r="BF3" t="n">
-        <v>2913815000</v>
+        <v>3852402000</v>
       </c>
       <c r="BG3" t="n">
-        <v>100521000</v>
+        <v>92000</v>
       </c>
       <c r="BH3" t="n">
-        <v>29000</v>
+        <v>404000</v>
       </c>
       <c r="BI3" t="n">
-        <v>51996000</v>
+        <v>64124000</v>
       </c>
       <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="n">
-        <v>49501000</v>
+        <v>68274000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2582000</v>
+        <v>10773000</v>
       </c>
       <c r="BN3" t="n">
-        <v>46919000</v>
+        <v>57501000</v>
       </c>
       <c r="BO3" t="n">
-        <v>46919000</v>
+        <v>57501000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>641498000</v>
@@ -1968,46 +1978,46 @@
         <v>641498000</v>
       </c>
       <c r="D4" t="n">
-        <v>2781117000</v>
+        <v>2174059000</v>
       </c>
       <c r="E4" t="n">
-        <v>2885583000</v>
+        <v>2271214000</v>
       </c>
       <c r="F4" t="n">
-        <v>1729525000</v>
+        <v>1430083000</v>
       </c>
       <c r="G4" t="n">
-        <v>4568143000</v>
+        <v>3651061000</v>
       </c>
       <c r="H4" t="n">
-        <v>797353000</v>
+        <v>730754000</v>
       </c>
       <c r="I4" t="n">
-        <v>1729525000</v>
+        <v>1430083000</v>
       </c>
       <c r="J4" t="n">
-        <v>46965000</v>
+        <v>50236000</v>
       </c>
       <c r="K4" t="n">
-        <v>1729525000</v>
+        <v>1430083000</v>
       </c>
       <c r="L4" t="n">
-        <v>1817733000</v>
+        <v>1525234000</v>
       </c>
       <c r="M4" t="n">
-        <v>1717330000</v>
+        <v>1414276000</v>
       </c>
       <c r="N4" t="n">
-        <v>-12195000</v>
+        <v>-15807000</v>
       </c>
       <c r="O4" t="n">
-        <v>1729525000</v>
+        <v>1430083000</v>
       </c>
       <c r="P4" t="n">
-        <v>516315000</v>
+        <v>516129000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1123329000</v>
+        <v>828920000</v>
       </c>
       <c r="R4" t="n">
         <v>233457000</v>
@@ -2019,144 +2029,142 @@
         <v>6415000</v>
       </c>
       <c r="U4" t="n">
-        <v>3390778000</v>
+        <v>2607928000</v>
       </c>
       <c r="V4" t="n">
-        <v>174919000</v>
+        <v>181578000</v>
       </c>
       <c r="W4" t="n">
-        <v>54691000</v>
+        <v>52156000</v>
       </c>
       <c r="X4" t="n">
-        <v>120228000</v>
+        <v>129422000</v>
       </c>
       <c r="Y4" t="n">
-        <v>32020000</v>
+        <v>34271000</v>
       </c>
       <c r="Z4" t="n">
-        <v>88208000</v>
+        <v>95151000</v>
       </c>
       <c r="AA4" t="n">
-        <v>3215859000</v>
+        <v>2426350000</v>
       </c>
       <c r="AB4" t="n">
-        <v>2765355000</v>
+        <v>2141792000</v>
       </c>
       <c r="AC4" t="n">
-        <v>14945000</v>
+        <v>15965000</v>
       </c>
       <c r="AD4" t="n">
-        <v>2750410000</v>
+        <v>2125827000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1780000</v>
+        <v>2442000</v>
       </c>
       <c r="AF4" t="n">
-        <v>227790000</v>
+        <v>141030000</v>
       </c>
       <c r="AG4" t="n">
-        <v>157508000</v>
+        <v>96513000</v>
       </c>
       <c r="AH4" t="n">
-        <v>14914000</v>
+        <v>330000</v>
       </c>
       <c r="AI4" t="n">
-        <v>55368000</v>
+        <v>44187000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5108108000</v>
+        <v>4022204000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1094896000</v>
+        <v>865100000</v>
       </c>
       <c r="AL4" t="n">
-        <v>102426000</v>
+        <v>3935000</v>
       </c>
       <c r="AM4" t="n">
-        <v>4029000</v>
+        <v>4377000</v>
       </c>
       <c r="AN4" t="n">
-        <v>6129000</v>
+        <v>5160000</v>
       </c>
       <c r="AO4" t="n">
-        <v>6129000</v>
+        <v>5160000</v>
       </c>
       <c r="AP4" t="n">
-        <v>15424000</v>
+        <v>9967000</v>
       </c>
       <c r="AQ4" t="n">
         <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>15424000</v>
+        <v>9967000</v>
       </c>
       <c r="AS4" t="n">
-        <v>883038000</v>
+        <v>776584000</v>
       </c>
       <c r="AT4" t="n">
-        <v>4745000</v>
+        <v>4957000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-14663000</v>
+        <v>-16982000</v>
       </c>
       <c r="AV4" t="n">
-        <v>19408000</v>
+        <v>21939000</v>
       </c>
       <c r="AW4" t="n">
-        <v>11038000</v>
+        <v>9048000</v>
       </c>
       <c r="AX4" t="n">
-        <v>8370000</v>
+        <v>12891000</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4013212000</v>
+        <v>3157104000</v>
       </c>
       <c r="BA4" t="n">
-        <v>17916000</v>
+        <v>31242000</v>
       </c>
       <c r="BB4" t="n">
         <v>10000000</v>
       </c>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>3852402000</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>10808000</v>
-      </c>
+        <v>2913815000</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
-        <v>3852402000</v>
+        <v>2913815000</v>
       </c>
       <c r="BG4" t="n">
-        <v>92000</v>
+        <v>100521000</v>
       </c>
       <c r="BH4" t="n">
-        <v>404000</v>
+        <v>29000</v>
       </c>
       <c r="BI4" t="n">
-        <v>64124000</v>
+        <v>51996000</v>
       </c>
       <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="n">
-        <v>68274000</v>
+        <v>49501000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10773000</v>
+        <v>2582000</v>
       </c>
       <c r="BN4" t="n">
-        <v>57501000</v>
+        <v>46919000</v>
       </c>
       <c r="BO4" t="n">
-        <v>57501000</v>
+        <v>46919000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>641498000</v>
@@ -2165,46 +2173,46 @@
         <v>641498000</v>
       </c>
       <c r="D5" t="n">
-        <v>3229715000</v>
+        <v>1270485000</v>
       </c>
       <c r="E5" t="n">
-        <v>3381231000</v>
+        <v>1344646000</v>
       </c>
       <c r="F5" t="n">
-        <v>1391955000</v>
+        <v>817538000</v>
       </c>
       <c r="G5" t="n">
-        <v>4715710000</v>
+        <v>2116878000</v>
       </c>
       <c r="H5" t="n">
-        <v>1545528000</v>
+        <v>95712000</v>
       </c>
       <c r="I5" t="n">
-        <v>1391955000</v>
+        <v>817538000</v>
       </c>
       <c r="J5" t="n">
-        <v>57476000</v>
+        <v>45306000</v>
       </c>
       <c r="K5" t="n">
-        <v>1391955000</v>
+        <v>817538000</v>
       </c>
       <c r="L5" t="n">
-        <v>2576056000</v>
+        <v>892449000</v>
       </c>
       <c r="M5" t="n">
-        <v>1382256000</v>
+        <v>801469000</v>
       </c>
       <c r="N5" t="n">
-        <v>-9699000</v>
+        <v>-16069000</v>
       </c>
       <c r="O5" t="n">
-        <v>1391955000</v>
+        <v>817538000</v>
       </c>
       <c r="P5" t="n">
-        <v>514124000</v>
+        <v>514667000</v>
       </c>
       <c r="Q5" t="n">
-        <v>791676000</v>
+        <v>225353000</v>
       </c>
       <c r="R5" t="n">
         <v>233457000</v>
@@ -2216,145 +2224,137 @@
         <v>6415000</v>
       </c>
       <c r="U5" t="n">
-        <v>3918848000</v>
+        <v>1675247000</v>
       </c>
       <c r="V5" t="n">
-        <v>1283710000</v>
+        <v>152001000</v>
       </c>
       <c r="W5" t="n">
-        <v>59839000</v>
+        <v>48417000</v>
       </c>
       <c r="X5" t="n">
-        <v>1223871000</v>
+        <v>103584000</v>
       </c>
       <c r="Y5" t="n">
-        <v>39770000</v>
+        <v>28673000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1184101000</v>
+        <v>74911000</v>
       </c>
       <c r="AA5" t="n">
-        <v>2635138000</v>
+        <v>1523246000</v>
       </c>
       <c r="AB5" t="n">
-        <v>2157360000</v>
+        <v>1241062000</v>
       </c>
       <c r="AC5" t="n">
-        <v>17706000</v>
+        <v>16633000</v>
       </c>
       <c r="AD5" t="n">
-        <v>2139654000</v>
+        <v>1224429000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2411000</v>
+        <v>1270000</v>
       </c>
       <c r="AF5" t="n">
-        <v>169336000</v>
+        <v>115714000</v>
       </c>
       <c r="AG5" t="n">
-        <v>142773000</v>
+        <v>82580000</v>
       </c>
       <c r="AH5" t="n">
-        <v>128000</v>
+        <v>258000</v>
       </c>
       <c r="AI5" t="n">
-        <v>26435000</v>
+        <v>32876000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5301104000</v>
+        <v>2476716000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1120438000</v>
+        <v>857758000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>3880000</v>
       </c>
       <c r="AM5" t="n">
-        <v>3005000</v>
+        <v>5627000</v>
       </c>
       <c r="AN5" t="n">
-        <v>6873000</v>
+        <v>53047000</v>
       </c>
       <c r="AO5" t="n">
-        <v>6873000</v>
+        <v>53047000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>6316000</v>
       </c>
       <c r="AQ5" t="n">
         <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>6316000</v>
       </c>
       <c r="AS5" t="n">
-        <v>1054096000</v>
+        <v>738379000</v>
       </c>
       <c r="AT5" t="n">
-        <v>3416000</v>
+        <v>2656000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-11629000</v>
+        <v>-19371000</v>
       </c>
       <c r="AV5" t="n">
-        <v>15045000</v>
+        <v>22027000</v>
       </c>
       <c r="AW5" t="n">
-        <v>7765000</v>
+        <v>9136000</v>
       </c>
       <c r="AX5" t="n">
-        <v>7280000</v>
+        <v>12891000</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4180666000</v>
+        <v>1618958000</v>
       </c>
       <c r="BA5" t="n">
-        <v>82243000</v>
+        <v>16223000</v>
       </c>
       <c r="BB5" t="n">
-        <v>10403000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>24402000</v>
-      </c>
+        <v>10000000</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>3878883000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7056000</v>
-      </c>
+        <v>1515764000</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
-        <v>3878883000</v>
+        <v>1515764000</v>
       </c>
       <c r="BG5" t="n">
-        <v>41897000</v>
+        <v>3000</v>
       </c>
       <c r="BH5" t="n">
-        <v>609000</v>
+        <v>29000</v>
       </c>
       <c r="BI5" t="n">
-        <v>5064000</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>-1617000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5064000</v>
-      </c>
+        <v>46132000</v>
+      </c>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="n">
-        <v>129008000</v>
+        <v>30807000</v>
       </c>
       <c r="BM5" t="n">
-        <v>34968000</v>
+        <v>1952000</v>
       </c>
       <c r="BN5" t="n">
-        <v>94040000</v>
+        <v>28855000</v>
       </c>
       <c r="BO5" t="n">
-        <v>94040000</v>
+        <v>28855000</v>
       </c>
     </row>
   </sheetData>
@@ -2625,594 +2625,594 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1023260000</v>
+        <v>-873132000</v>
       </c>
       <c r="C2" t="n">
-        <v>-938656000</v>
+        <v>-518915000</v>
       </c>
       <c r="D2" t="n">
-        <v>109537000</v>
+        <v>1454646000</v>
       </c>
       <c r="E2" t="n">
-        <v>-115000</v>
+        <v>-1571000</v>
       </c>
       <c r="F2" t="n">
-        <v>28855000</v>
+        <v>94040000</v>
       </c>
       <c r="G2" t="n">
-        <v>46919000</v>
+        <v>55457000</v>
       </c>
       <c r="H2" t="n">
-        <v>-364000</v>
+        <v>-2837000</v>
       </c>
       <c r="I2" t="n">
-        <v>-17700000</v>
+        <v>41420000</v>
       </c>
       <c r="J2" t="n">
-        <v>-1031789000</v>
+        <v>901511000</v>
       </c>
       <c r="K2" t="n">
-        <v>-7813000</v>
+        <v>68854000</v>
       </c>
       <c r="L2" t="n">
-        <v>-173982000</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
+        <v>-84192000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
       <c r="N2" t="n">
-        <v>-829119000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+        <v>935731000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>935731000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-518915000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1454646000</v>
+      </c>
       <c r="R2" t="n">
-        <v>-829119000</v>
+        <v>935731000</v>
       </c>
       <c r="S2" t="n">
-        <v>-938656000</v>
+        <v>-518915000</v>
       </c>
       <c r="T2" t="n">
-        <v>109537000</v>
+        <v>1454646000</v>
       </c>
       <c r="U2" t="n">
-        <v>-9286000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
+        <v>11470000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-22000</v>
+      </c>
       <c r="W2" t="n">
-        <v>571000</v>
+        <v>206000</v>
       </c>
       <c r="X2" t="n">
-        <v>-9496000</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" t="n">
-        <v>-9496000</v>
-      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>-246000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>-39133000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>19000000</v>
+      </c>
       <c r="AC2" t="n">
-        <v>-246000</v>
+        <v>-58133000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>51750000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>51750000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
       <c r="AG2" t="n">
-        <v>-115000</v>
+        <v>-1331000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-115000</v>
+        <v>-1571000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1023375000</v>
+        <v>-871561000</v>
       </c>
       <c r="AK2" t="n">
-        <v>28000</v>
+        <v>-3131000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1242117000</v>
+        <v>-853521000</v>
       </c>
       <c r="AM2" t="n">
-        <v>15881000</v>
+        <v>55123000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-5084000</v>
+        <v>84109000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1212372000</v>
+        <v>-1051964000</v>
       </c>
       <c r="AP2" t="n">
-        <v>18948000</v>
+        <v>59211000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>141063000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>11311000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>9541000</v>
+      </c>
       <c r="AS2" t="n">
-        <v>2402000</v>
+        <v>3434000</v>
       </c>
       <c r="AT2" t="n">
-        <v>2402000</v>
+        <v>3434000</v>
       </c>
       <c r="AU2" t="n">
-        <v>67413000</v>
+        <v>8450000</v>
       </c>
       <c r="AV2" t="n">
-        <v>-5727000</v>
+        <v>-10357000</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>430000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-241000</v>
+        <v>-2168000</v>
       </c>
       <c r="AY2" t="n">
-        <v>-610380000</v>
+        <v>-36001000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>845066000</v>
+        <v>802138000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1888164000</v>
+        <v>-1355298000</v>
       </c>
       <c r="D3" t="n">
-        <v>1265258000</v>
+        <v>810142000</v>
       </c>
       <c r="E3" t="n">
-        <v>-738000</v>
+        <v>-4781000</v>
       </c>
       <c r="F3" t="n">
-        <v>46919000</v>
+        <v>57501000</v>
       </c>
       <c r="G3" t="n">
-        <v>57501000</v>
+        <v>94040000</v>
       </c>
       <c r="H3" t="n">
-        <v>-458000</v>
+        <v>-1600000</v>
       </c>
       <c r="I3" t="n">
-        <v>-10124000</v>
+        <v>-34939000</v>
       </c>
       <c r="J3" t="n">
-        <v>-919728000</v>
+        <v>-711775000</v>
       </c>
       <c r="K3" t="n">
-        <v>-61433000</v>
+        <v>22530000</v>
       </c>
       <c r="L3" t="n">
-        <v>-214762000</v>
+        <v>-167569000</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>-622906000</v>
+        <v>-545156000</v>
       </c>
       <c r="O3" t="n">
-        <v>-622906000</v>
+        <v>-545156000</v>
       </c>
       <c r="P3" t="n">
-        <v>-1888164000</v>
+        <v>-1355298000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1265258000</v>
+        <v>810142000</v>
       </c>
       <c r="R3" t="n">
-        <v>-622906000</v>
+        <v>-545156000</v>
       </c>
       <c r="S3" t="n">
-        <v>-1888164000</v>
+        <v>-1355298000</v>
       </c>
       <c r="T3" t="n">
-        <v>1265258000</v>
+        <v>810142000</v>
       </c>
       <c r="U3" t="n">
-        <v>63800000</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
+        <v>-130083000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-101388000</v>
+      </c>
       <c r="W3" t="n">
-        <v>2832000</v>
+        <v>411000</v>
       </c>
       <c r="X3" t="n">
-        <v>2103000</v>
+        <v>1366000</v>
       </c>
       <c r="Y3" t="n">
-        <v>2103000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
+        <v>1366000</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>-860000</v>
+        <v>-9864000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>6400000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-860000</v>
+        <v>-16264000</v>
       </c>
       <c r="AD3" t="n">
-        <v>58000000</v>
+        <v>-15827000</v>
       </c>
       <c r="AE3" t="n">
-        <v>58000000</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>-15827000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1725000</v>
+        <v>-4781000</v>
       </c>
       <c r="AH3" t="n">
-        <v>2463000</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-738000</v>
+        <v>-4781000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>845804000</v>
+        <v>806919000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-14125000</v>
+        <v>-32982000</v>
       </c>
       <c r="AL3" t="n">
-        <v>964367000</v>
+        <v>438614000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-19585000</v>
+        <v>-53634000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-81176000</v>
+        <v>120424000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1041820000</v>
+        <v>382983000</v>
       </c>
       <c r="AP3" t="n">
-        <v>23308000</v>
+        <v>-11159000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>91162000</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>19045000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
       <c r="AS3" t="n">
-        <v>2687000</v>
+        <v>4434000</v>
       </c>
       <c r="AT3" t="n">
-        <v>2687000</v>
+        <v>4434000</v>
       </c>
       <c r="AU3" t="n">
-        <v>73099000</v>
+        <v>14247000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-2488000</v>
+        <v>-9431000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-107000</v>
+        <v>34000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-1488000</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>-301174000</v>
+        <v>372784000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>802138000</v>
+        <v>845066000</v>
       </c>
       <c r="C4" t="n">
-        <v>-1355298000</v>
+        <v>-1888164000</v>
       </c>
       <c r="D4" t="n">
-        <v>810142000</v>
+        <v>1265258000</v>
       </c>
       <c r="E4" t="n">
-        <v>-4781000</v>
+        <v>-738000</v>
       </c>
       <c r="F4" t="n">
+        <v>46919000</v>
+      </c>
+      <c r="G4" t="n">
         <v>57501000</v>
       </c>
-      <c r="G4" t="n">
-        <v>94040000</v>
-      </c>
       <c r="H4" t="n">
-        <v>-1600000</v>
+        <v>-458000</v>
       </c>
       <c r="I4" t="n">
-        <v>-34939000</v>
+        <v>-10124000</v>
       </c>
       <c r="J4" t="n">
-        <v>-711775000</v>
+        <v>-919728000</v>
       </c>
       <c r="K4" t="n">
-        <v>22530000</v>
+        <v>-61433000</v>
       </c>
       <c r="L4" t="n">
-        <v>-167569000</v>
+        <v>-214762000</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>-545156000</v>
+        <v>-622906000</v>
       </c>
       <c r="O4" t="n">
-        <v>-545156000</v>
+        <v>-622906000</v>
       </c>
       <c r="P4" t="n">
-        <v>-1355298000</v>
+        <v>-1888164000</v>
       </c>
       <c r="Q4" t="n">
-        <v>810142000</v>
+        <v>1265258000</v>
       </c>
       <c r="R4" t="n">
-        <v>-545156000</v>
+        <v>-622906000</v>
       </c>
       <c r="S4" t="n">
-        <v>-1355298000</v>
+        <v>-1888164000</v>
       </c>
       <c r="T4" t="n">
-        <v>810142000</v>
+        <v>1265258000</v>
       </c>
       <c r="U4" t="n">
-        <v>-130083000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-101388000</v>
-      </c>
+        <v>63800000</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>411000</v>
+        <v>2832000</v>
       </c>
       <c r="X4" t="n">
-        <v>1366000</v>
+        <v>2103000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1366000</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+        <v>2103000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
       <c r="AA4" t="n">
-        <v>-9864000</v>
+        <v>-860000</v>
       </c>
       <c r="AB4" t="n">
-        <v>6400000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-16264000</v>
+        <v>-860000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-15827000</v>
+        <v>58000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>58000000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-15827000</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>-4781000</v>
+        <v>1725000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2463000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-4781000</v>
+        <v>-738000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>806919000</v>
+        <v>845804000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-32982000</v>
+        <v>-14125000</v>
       </c>
       <c r="AL4" t="n">
-        <v>438614000</v>
+        <v>964367000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-53634000</v>
+        <v>-19585000</v>
       </c>
       <c r="AN4" t="n">
-        <v>120424000</v>
+        <v>-81176000</v>
       </c>
       <c r="AO4" t="n">
-        <v>382983000</v>
+        <v>1041820000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-11159000</v>
+        <v>23308000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19045000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
+        <v>91162000</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>4434000</v>
+        <v>2687000</v>
       </c>
       <c r="AT4" t="n">
-        <v>4434000</v>
+        <v>2687000</v>
       </c>
       <c r="AU4" t="n">
-        <v>14247000</v>
+        <v>73099000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-9431000</v>
+        <v>-2488000</v>
       </c>
       <c r="AW4" t="n">
-        <v>34000</v>
+        <v>-107000</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>-1488000</v>
       </c>
       <c r="AY4" t="n">
-        <v>372784000</v>
+        <v>-301174000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-873132000</v>
+        <v>1023260000</v>
       </c>
       <c r="C5" t="n">
-        <v>-518915000</v>
+        <v>-938656000</v>
       </c>
       <c r="D5" t="n">
-        <v>1454646000</v>
+        <v>109537000</v>
       </c>
       <c r="E5" t="n">
-        <v>-1571000</v>
+        <v>-115000</v>
       </c>
       <c r="F5" t="n">
-        <v>94040000</v>
+        <v>28855000</v>
       </c>
       <c r="G5" t="n">
-        <v>55457000</v>
+        <v>46919000</v>
       </c>
       <c r="H5" t="n">
-        <v>-2837000</v>
+        <v>-364000</v>
       </c>
       <c r="I5" t="n">
-        <v>41420000</v>
+        <v>-17700000</v>
       </c>
       <c r="J5" t="n">
-        <v>901511000</v>
+        <v>-1031789000</v>
       </c>
       <c r="K5" t="n">
-        <v>68854000</v>
+        <v>-7813000</v>
       </c>
       <c r="L5" t="n">
-        <v>-84192000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
+        <v>-173982000</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>935731000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>935731000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-518915000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1454646000</v>
-      </c>
+        <v>-829119000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>935731000</v>
+        <v>-829119000</v>
       </c>
       <c r="S5" t="n">
-        <v>-518915000</v>
+        <v>-938656000</v>
       </c>
       <c r="T5" t="n">
-        <v>1454646000</v>
+        <v>109537000</v>
       </c>
       <c r="U5" t="n">
-        <v>11470000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-22000</v>
-      </c>
+        <v>-9286000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>206000</v>
+        <v>571000</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-9496000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>-9496000</v>
+      </c>
       <c r="AA5" t="n">
-        <v>-39133000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>19000000</v>
-      </c>
+        <v>-246000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>-58133000</v>
+        <v>-246000</v>
       </c>
       <c r="AD5" t="n">
-        <v>51750000</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>51750000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>-1331000</v>
+        <v>-115000</v>
       </c>
       <c r="AH5" t="n">
-        <v>240000</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1571000</v>
+        <v>-115000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-871561000</v>
+        <v>1023375000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-3131000</v>
+        <v>28000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-853521000</v>
+        <v>1242117000</v>
       </c>
       <c r="AM5" t="n">
-        <v>55123000</v>
+        <v>15881000</v>
       </c>
       <c r="AN5" t="n">
-        <v>84109000</v>
+        <v>-5084000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1051964000</v>
+        <v>1212372000</v>
       </c>
       <c r="AP5" t="n">
-        <v>59211000</v>
+        <v>18948000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11311000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>9541000</v>
-      </c>
+        <v>141063000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>3434000</v>
+        <v>2402000</v>
       </c>
       <c r="AT5" t="n">
-        <v>3434000</v>
+        <v>2402000</v>
       </c>
       <c r="AU5" t="n">
-        <v>8450000</v>
+        <v>67413000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-10357000</v>
+        <v>-5727000</v>
       </c>
       <c r="AW5" t="n">
-        <v>430000</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-2168000</v>
+        <v>-241000</v>
       </c>
       <c r="AY5" t="n">
-        <v>-36001000</v>
+        <v>-610380000</v>
       </c>
     </row>
   </sheetData>
@@ -3752,197 +3752,197 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EN1" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Man Fai  Chan', 'age': 66, 'title': 'Executive Chairman &amp; CEO', 'yearBorn': 1959, 'fiscalYear': 2025, 'totalPay': 2894000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wai Shuen  Cheung HKICS', 'age': 50, 'title': 'Vice Chairman &amp; Company Secretary', 'yearBorn': 1975, 'fiscalYear': 2025, 'totalPay': 1341000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Lap Yan  Lee', 'age': 54, 'title': 'Managing Director of Project Development - Star Properties', 'yearBorn': 1971, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bobby Jump  Yu', 'age': 36, 'title': 'Managing Director of Capital Market - Star Properties', 'yearBorn': 1989, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Man Fai  Chan', 'age': 66, 'title': 'Executive Chairman &amp; CEO', 'yearBorn': 1959, 'fiscalYear': 2025, 'totalPay': 2894000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wai Shuen  Cheung HKICS', 'age': 50, 'title': 'Vice Chairman &amp; Company Secretary', 'yearBorn': 1975, 'fiscalYear': 2025, 'totalPay': 1341000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Lap Yan  Lee', 'age': 54, 'title': 'MD of Project Development - Star Properties &amp; Executive Director', 'yearBorn': 1971, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Bobby Jump  Yu', 'age': 36, 'title': 'Managing Director of Capital Market - Star Properties', 'yearBorn': 1989, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4045,28 +4045,28 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.123</v>
+        <v>0.146</v>
       </c>
       <c r="V2" t="n">
-        <v>0.121</v>
+        <v>0.145</v>
       </c>
       <c r="W2" t="n">
-        <v>0.121</v>
+        <v>0.145</v>
       </c>
       <c r="X2" t="n">
-        <v>0.121</v>
+        <v>0.145</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.123</v>
+        <v>0.146</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.121</v>
+        <v>0.145</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.121</v>
+        <v>0.145</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.121</v>
+        <v>0.145</v>
       </c>
       <c r="AC2" t="n">
         <v>1602460800</v>
@@ -4075,28 +4075,28 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.09</v>
+        <v>0.102</v>
       </c>
       <c r="AF2" t="n">
-        <v>124000</v>
+        <v>14000</v>
       </c>
       <c r="AG2" t="n">
-        <v>124000</v>
+        <v>14000</v>
       </c>
       <c r="AH2" t="n">
-        <v>69146</v>
+        <v>53233</v>
       </c>
       <c r="AI2" t="n">
-        <v>12400</v>
+        <v>24800</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12400</v>
+        <v>24800</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.12</v>
+        <v>0.142</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.14</v>
+        <v>0.145</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -4105,13 +4105,13 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>78904256</v>
+        <v>93017208</v>
       </c>
       <c r="AP2" t="n">
-        <v>78904254</v>
+        <v>93658708</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.092</v>
+        <v>0.096</v>
       </c>
       <c r="AR2" t="n">
         <v>0.18</v>
@@ -4123,13 +4123,13 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.41019696</v>
+        <v>0.4835655</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.13692</v>
+        <v>0.13078</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.13111</v>
+        <v>0.130385</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -4146,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1339607296</v>
+        <v>1353720192</v>
       </c>
       <c r="BC2" t="n">
         <v>-1.39413</v>
@@ -4170,7 +4170,7 @@
         <v>0.862</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.14269142</v>
+        <v>0.16821346</v>
       </c>
       <c r="BK2" t="n">
         <v>1767139200</v>
@@ -4196,16 +4196,16 @@
         <v>1493856000</v>
       </c>
       <c r="BR2" t="n">
-        <v>6.964</v>
+        <v>7.038</v>
       </c>
       <c r="BS2" t="n">
-        <v>-52.703</v>
+        <v>-53.258</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.3225807</v>
+        <v>0.48979592</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="n">
         <v>0.02</v>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="BY2" t="n">
-        <v>0.123</v>
+        <v>0.145</v>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
@@ -4318,150 +4318,150 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DA2" t="n">
+        <v>-0.001000002</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>0.145 - 0.145</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>53233</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.048999995</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>0.5104166</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>0.096 - 0.18</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.03500001</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.19444449</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>48.97959</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1743172336</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1743172336</v>
+      </c>
+      <c r="DM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1468373400000</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.6849329</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.014219999</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.108732216</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0.014614999</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.11209111</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>Star Properties Group (Cayman Islands) Limited</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EC2" t="n">
+        <v>1782099800</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>finmb_370014183</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="EH2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>STAR GROUP ASIA</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>Star Group Asia Limited</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
         <is>
           <t>PRE</t>
         </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>finmb_370014183</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DF2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>STAR GROUP ASIA</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>Star Group Asia Limited</t>
-        </is>
-      </c>
-      <c r="DK2" t="n">
-        <v>69146</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.031000003</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.33695656</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>0.092 - 0.18</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.057000004</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.31666666</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>32.258068</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>1743172336</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1743172336</v>
-      </c>
-      <c r="DT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.013920002</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.10166521</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.008109994000000001</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.061856415</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>Star Properties Group (Cayman Islands) Limited</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="ED2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1468373400000</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>0.121 - 0.121</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EK2" t="n">
-        <v>1779776427</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0.123</v>
       </c>
       <c r="EN2" t="inlineStr"/>
     </row>
